--- a/downloads/Kroger-Experis-Rate-Card-2026.xlsx
+++ b/downloads/Kroger-Experis-Rate-Card-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://manpowergroupapps-my.sharepoint.com/personal/paige_beasley_experis_com/Documents/Desktop/2026 Kroger/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA4319CE-0C0B-4994-A4C4-EF88FFF59E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF9230D8-915C-4129-AE56-6CD43D2733E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E354ADE5-0CB8-43AA-9C37-43E064C7542A}"/>
   </bookViews>
@@ -40,15 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="416">
   <si>
     <t>Current Rate Card</t>
   </si>
   <si>
     <t>Moving Forward</t>
-  </si>
-  <si>
-    <t>10% Rate Reduction</t>
   </si>
   <si>
     <t>Onshore</t>
@@ -2210,46 +2207,44 @@
         <v>1</v>
       </c>
       <c r="F2" s="45"/>
-      <c r="H2" s="43" t="s">
-        <v>2</v>
-      </c>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="2:8" ht="15" thickBot="1">
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
       <c r="D3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="33" t="s">
         <v>3</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="23.1" customHeight="1" thickBot="1">
       <c r="B4" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="32" t="s">
-        <v>7</v>
-      </c>
       <c r="E4" s="41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>9</v>
       </c>
       <c r="D5" s="31">
         <v>165</v>
@@ -2263,10 +2258,10 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>10</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>11</v>
       </c>
       <c r="D6" s="29">
         <v>180</v>
@@ -2280,10 +2275,10 @@
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>12</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>13</v>
       </c>
       <c r="D7" s="29">
         <v>200</v>
@@ -2297,10 +2292,10 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>14</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>15</v>
       </c>
       <c r="D8" s="29">
         <v>220</v>
@@ -2314,10 +2309,10 @@
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>17</v>
       </c>
       <c r="D9" s="29">
         <v>50</v>
@@ -2331,10 +2326,10 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>18</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>19</v>
       </c>
       <c r="D10" s="29">
         <v>65</v>
@@ -2348,10 +2343,10 @@
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>20</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>21</v>
       </c>
       <c r="D11" s="29">
         <v>80</v>
@@ -2365,10 +2360,10 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>22</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>23</v>
       </c>
       <c r="D12" s="29">
         <v>95</v>
@@ -2382,10 +2377,10 @@
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>24</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>25</v>
       </c>
       <c r="D13" s="29">
         <v>130</v>
@@ -2394,15 +2389,15 @@
         <v>118.18181818181817</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>27</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>28</v>
       </c>
       <c r="D14" s="29">
         <v>140</v>
@@ -2416,10 +2411,10 @@
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>29</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>30</v>
       </c>
       <c r="D15" s="29">
         <v>150</v>
@@ -2433,10 +2428,10 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>31</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>32</v>
       </c>
       <c r="D16" s="29">
         <v>175</v>
@@ -2450,10 +2445,10 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>34</v>
       </c>
       <c r="D17" s="29">
         <v>75</v>
@@ -2467,10 +2462,10 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="D18" s="29">
         <v>95</v>
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>37</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>38</v>
       </c>
       <c r="D19" s="29">
         <v>115</v>
@@ -2501,10 +2496,10 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>39</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>40</v>
       </c>
       <c r="D20" s="29">
         <v>135</v>
@@ -2518,10 +2513,10 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>41</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>42</v>
       </c>
       <c r="D21" s="29">
         <v>115</v>
@@ -2535,10 +2530,10 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>43</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>44</v>
       </c>
       <c r="D22" s="29">
         <v>125</v>
@@ -2552,10 +2547,10 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>45</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>46</v>
       </c>
       <c r="D23" s="29">
         <v>135</v>
@@ -2569,10 +2564,10 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>47</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>48</v>
       </c>
       <c r="D24" s="29">
         <v>150</v>
@@ -2586,10 +2581,10 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="29">
         <v>105</v>
@@ -2603,10 +2598,10 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="25" t="s">
         <v>51</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>52</v>
       </c>
       <c r="D26" s="29">
         <v>125</v>
@@ -2620,10 +2615,10 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>53</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>54</v>
       </c>
       <c r="D27" s="29">
         <v>145</v>
@@ -2637,10 +2632,10 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="25" t="s">
         <v>55</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>56</v>
       </c>
       <c r="D28" s="29">
         <v>165</v>
@@ -2654,10 +2649,10 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>57</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>58</v>
       </c>
       <c r="D29" s="29">
         <v>108</v>
@@ -2671,10 +2666,10 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="25" t="s">
         <v>59</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>60</v>
       </c>
       <c r="D30" s="29">
         <v>119</v>
@@ -2688,10 +2683,10 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="25" t="s">
         <v>61</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>62</v>
       </c>
       <c r="D31" s="29">
         <v>134</v>
@@ -2705,10 +2700,10 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="25" t="s">
         <v>63</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>64</v>
       </c>
       <c r="D32" s="29">
         <v>145</v>
@@ -2722,10 +2717,10 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>65</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>66</v>
       </c>
       <c r="D33" s="29">
         <v>108</v>
@@ -2739,10 +2734,10 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>67</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>68</v>
       </c>
       <c r="D34" s="29">
         <v>115</v>
@@ -2756,10 +2751,10 @@
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="25" t="s">
         <v>69</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>70</v>
       </c>
       <c r="D35" s="29">
         <v>135</v>
@@ -2773,10 +2768,10 @@
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="25" t="s">
         <v>71</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>72</v>
       </c>
       <c r="D36" s="29">
         <v>145</v>
@@ -2790,10 +2785,10 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>73</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>74</v>
       </c>
       <c r="D37" s="29">
         <v>80</v>
@@ -2807,10 +2802,10 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="25" t="s">
         <v>75</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>76</v>
       </c>
       <c r="D38" s="29">
         <v>90</v>
@@ -2824,10 +2819,10 @@
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="25" t="s">
         <v>77</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>78</v>
       </c>
       <c r="D39" s="29">
         <v>100</v>
@@ -2841,10 +2836,10 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="25" t="s">
         <v>79</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>80</v>
       </c>
       <c r="D40" s="29">
         <v>110</v>
@@ -2858,10 +2853,10 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="25" t="s">
         <v>81</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>82</v>
       </c>
       <c r="D41" s="29">
         <v>65</v>
@@ -2875,10 +2870,10 @@
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>83</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>84</v>
       </c>
       <c r="D42" s="29">
         <v>100</v>
@@ -2892,10 +2887,10 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="25" t="s">
         <v>85</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>86</v>
       </c>
       <c r="D43" s="29">
         <v>115</v>
@@ -2909,10 +2904,10 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>88</v>
       </c>
       <c r="D44" s="29">
         <v>130</v>
@@ -2926,10 +2921,10 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="D45" s="29">
         <v>100</v>
@@ -2943,10 +2938,10 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="25" t="s">
         <v>91</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>92</v>
       </c>
       <c r="D46" s="29">
         <v>115</v>
@@ -2960,10 +2955,10 @@
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="25" t="s">
         <v>93</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>94</v>
       </c>
       <c r="D47" s="29">
         <v>135</v>
@@ -2977,10 +2972,10 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>95</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>96</v>
       </c>
       <c r="D48" s="29">
         <v>150</v>
@@ -2994,10 +2989,10 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="25" t="s">
         <v>97</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>98</v>
       </c>
       <c r="D49" s="29">
         <v>90</v>
@@ -3011,10 +3006,10 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>100</v>
       </c>
       <c r="D50" s="29">
         <v>122</v>
@@ -3028,10 +3023,10 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="25" t="s">
         <v>101</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>102</v>
       </c>
       <c r="D51" s="29">
         <v>132</v>
@@ -3045,10 +3040,10 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="25" t="s">
         <v>103</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>104</v>
       </c>
       <c r="D52" s="29">
         <v>145</v>
@@ -3062,10 +3057,10 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="25" t="s">
         <v>105</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>106</v>
       </c>
       <c r="D53" s="29">
         <v>80</v>
@@ -3079,10 +3074,10 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="25" t="s">
         <v>107</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>108</v>
       </c>
       <c r="D54" s="29">
         <v>100</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="25" t="s">
         <v>109</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>110</v>
       </c>
       <c r="D55" s="29">
         <v>125</v>
@@ -3113,10 +3108,10 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="25" t="s">
         <v>111</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>112</v>
       </c>
       <c r="D56" s="29">
         <v>140</v>
@@ -3130,10 +3125,10 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="25" t="s">
         <v>113</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>114</v>
       </c>
       <c r="D57" s="29">
         <v>90</v>
@@ -3147,10 +3142,10 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="25" t="s">
         <v>115</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>116</v>
       </c>
       <c r="D58" s="29">
         <v>100</v>
@@ -3164,10 +3159,10 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="25" t="s">
         <v>117</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>118</v>
       </c>
       <c r="D59" s="29">
         <v>110</v>
@@ -3181,10 +3176,10 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="25" t="s">
         <v>119</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>120</v>
       </c>
       <c r="D60" s="29">
         <v>120</v>
@@ -3198,10 +3193,10 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="25" t="s">
         <v>121</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>122</v>
       </c>
       <c r="D61" s="29">
         <v>125</v>
@@ -3210,15 +3205,15 @@
         <v>113.63636363636363</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="25" t="s">
         <v>123</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>124</v>
       </c>
       <c r="D62" s="29">
         <v>150</v>
@@ -3232,10 +3227,10 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="25" t="s">
         <v>125</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>126</v>
       </c>
       <c r="D63" s="29">
         <v>175</v>
@@ -3249,10 +3244,10 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="25" t="s">
         <v>127</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>128</v>
       </c>
       <c r="D64" s="29">
         <v>200</v>
@@ -3266,10 +3261,10 @@
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="25" t="s">
         <v>129</v>
-      </c>
-      <c r="C65" s="25" t="s">
-        <v>130</v>
       </c>
       <c r="D65" s="29">
         <v>70</v>
@@ -3283,10 +3278,10 @@
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="25" t="s">
         <v>131</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>132</v>
       </c>
       <c r="D66" s="29">
         <v>80</v>
@@ -3300,10 +3295,10 @@
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="25" t="s">
         <v>133</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>134</v>
       </c>
       <c r="D67" s="29">
         <v>95</v>
@@ -3317,10 +3312,10 @@
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="25" t="s">
         <v>135</v>
-      </c>
-      <c r="C68" s="25" t="s">
-        <v>136</v>
       </c>
       <c r="D68" s="29">
         <v>110</v>
@@ -3334,10 +3329,10 @@
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>137</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>138</v>
       </c>
       <c r="D69" s="29">
         <v>165</v>
@@ -3351,10 +3346,10 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="25" t="s">
         <v>139</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>140</v>
       </c>
       <c r="D70" s="29">
         <v>180</v>
@@ -3368,10 +3363,10 @@
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" s="25" t="s">
         <v>141</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>142</v>
       </c>
       <c r="D71" s="29">
         <v>200</v>
@@ -3385,10 +3380,10 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="25" t="s">
         <v>143</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>144</v>
       </c>
       <c r="D72" s="29">
         <v>220</v>
@@ -3402,10 +3397,10 @@
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" s="25" t="s">
         <v>145</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>146</v>
       </c>
       <c r="D73" s="29">
         <v>105</v>
@@ -3419,10 +3414,10 @@
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="D74" s="29">
         <v>115</v>
@@ -3436,10 +3431,10 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C75" s="25" t="s">
         <v>149</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>150</v>
       </c>
       <c r="D75" s="29">
         <v>128</v>
@@ -3453,10 +3448,10 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="25" t="s">
         <v>151</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>152</v>
       </c>
       <c r="D76" s="29">
         <v>138</v>
@@ -3470,10 +3465,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" s="25" t="s">
         <v>153</v>
-      </c>
-      <c r="C77" s="25" t="s">
-        <v>154</v>
       </c>
       <c r="D77" s="29">
         <v>95</v>
@@ -3487,10 +3482,10 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" s="25" t="s">
         <v>155</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>156</v>
       </c>
       <c r="D78" s="29">
         <v>110</v>
@@ -3504,10 +3499,10 @@
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C79" s="25" t="s">
         <v>157</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>158</v>
       </c>
       <c r="D79" s="29">
         <v>125</v>
@@ -3521,10 +3516,10 @@
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" s="25" t="s">
         <v>159</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>160</v>
       </c>
       <c r="D80" s="29">
         <v>140</v>
@@ -3538,10 +3533,10 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="25" t="s">
         <v>161</v>
-      </c>
-      <c r="C81" s="25" t="s">
-        <v>162</v>
       </c>
       <c r="D81" s="29">
         <v>110</v>
@@ -3555,10 +3550,10 @@
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" s="25" t="s">
         <v>163</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>164</v>
       </c>
       <c r="D82" s="29">
         <v>122</v>
@@ -3572,10 +3567,10 @@
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" s="25" t="s">
         <v>165</v>
-      </c>
-      <c r="C83" s="25" t="s">
-        <v>166</v>
       </c>
       <c r="D83" s="29">
         <v>132</v>
@@ -3589,10 +3584,10 @@
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" s="25" t="s">
         <v>167</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>168</v>
       </c>
       <c r="D84" s="29">
         <v>145</v>
@@ -3606,10 +3601,10 @@
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>169</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>170</v>
       </c>
       <c r="D85" s="29">
         <v>105</v>
@@ -3623,10 +3618,10 @@
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="25" t="s">
         <v>171</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>172</v>
       </c>
       <c r="D86" s="29">
         <v>110</v>
@@ -3640,10 +3635,10 @@
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C87" s="25" t="s">
         <v>173</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>174</v>
       </c>
       <c r="D87" s="29">
         <v>120</v>
@@ -3657,10 +3652,10 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" s="25" t="s">
         <v>175</v>
-      </c>
-      <c r="C88" s="25" t="s">
-        <v>176</v>
       </c>
       <c r="D88" s="29">
         <v>135</v>
@@ -3674,10 +3669,10 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="C89" s="25" t="s">
         <v>177</v>
-      </c>
-      <c r="C89" s="25" t="s">
-        <v>178</v>
       </c>
       <c r="D89" s="29">
         <v>95</v>
@@ -3691,10 +3686,10 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C90" s="25" t="s">
         <v>179</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>180</v>
       </c>
       <c r="D90" s="29">
         <v>110</v>
@@ -3708,10 +3703,10 @@
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" s="25" t="s">
         <v>181</v>
-      </c>
-      <c r="C91" s="25" t="s">
-        <v>182</v>
       </c>
       <c r="D91" s="29">
         <v>127</v>
@@ -3725,10 +3720,10 @@
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C92" s="25" t="s">
         <v>183</v>
-      </c>
-      <c r="C92" s="25" t="s">
-        <v>184</v>
       </c>
       <c r="D92" s="29">
         <v>140</v>
@@ -3742,10 +3737,10 @@
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D93" s="29">
         <v>105</v>
@@ -3759,10 +3754,10 @@
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D94" s="29">
         <v>110</v>
@@ -3776,10 +3771,10 @@
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D95" s="29">
         <v>120</v>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D96" s="29">
         <v>135</v>
@@ -3810,10 +3805,10 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C97" s="25" t="s">
         <v>189</v>
-      </c>
-      <c r="C97" s="25" t="s">
-        <v>190</v>
       </c>
       <c r="D97" s="29">
         <v>108</v>
@@ -3827,10 +3822,10 @@
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C98" s="25" t="s">
         <v>191</v>
-      </c>
-      <c r="C98" s="25" t="s">
-        <v>192</v>
       </c>
       <c r="D98" s="29">
         <v>119</v>
@@ -3844,10 +3839,10 @@
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="C99" s="25" t="s">
         <v>193</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>194</v>
       </c>
       <c r="D99" s="29">
         <v>134</v>
@@ -3861,10 +3856,10 @@
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C100" s="25" t="s">
         <v>195</v>
-      </c>
-      <c r="C100" s="25" t="s">
-        <v>196</v>
       </c>
       <c r="D100" s="29">
         <v>145</v>
@@ -3878,10 +3873,10 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C101" s="25" t="s">
         <v>197</v>
-      </c>
-      <c r="C101" s="25" t="s">
-        <v>198</v>
       </c>
       <c r="D101" s="29">
         <v>120</v>
@@ -3890,15 +3885,15 @@
         <v>109.09090909090908</v>
       </c>
       <c r="F101" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C102" s="25" t="s">
         <v>199</v>
-      </c>
-      <c r="C102" s="25" t="s">
-        <v>200</v>
       </c>
       <c r="D102" s="29">
         <v>160</v>
@@ -3912,10 +3907,10 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="C103" s="25" t="s">
         <v>201</v>
-      </c>
-      <c r="C103" s="25" t="s">
-        <v>202</v>
       </c>
       <c r="D103" s="29">
         <v>180</v>
@@ -3929,10 +3924,10 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="C104" s="25" t="s">
         <v>203</v>
-      </c>
-      <c r="C104" s="25" t="s">
-        <v>204</v>
       </c>
       <c r="D104" s="29">
         <v>200</v>
@@ -3946,10 +3941,10 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C105" s="25" t="s">
         <v>205</v>
-      </c>
-      <c r="C105" s="25" t="s">
-        <v>206</v>
       </c>
       <c r="D105" s="29">
         <v>95</v>
@@ -3963,10 +3958,10 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="C106" s="25" t="s">
         <v>207</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>208</v>
       </c>
       <c r="D106" s="29">
         <v>110</v>
@@ -3980,10 +3975,10 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="C107" s="25" t="s">
         <v>209</v>
-      </c>
-      <c r="C107" s="25" t="s">
-        <v>210</v>
       </c>
       <c r="D107" s="29">
         <v>125</v>
@@ -3997,10 +3992,10 @@
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C108" s="25" t="s">
         <v>211</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>212</v>
       </c>
       <c r="D108" s="29">
         <v>140</v>
@@ -4014,10 +4009,10 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="C109" s="25" t="s">
         <v>213</v>
-      </c>
-      <c r="C109" s="25" t="s">
-        <v>214</v>
       </c>
       <c r="D109" s="29">
         <v>80</v>
@@ -4031,10 +4026,10 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="C110" s="25" t="s">
         <v>215</v>
-      </c>
-      <c r="C110" s="25" t="s">
-        <v>216</v>
       </c>
       <c r="D110" s="29">
         <v>100</v>
@@ -4048,10 +4043,10 @@
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C111" s="25" t="s">
         <v>217</v>
-      </c>
-      <c r="C111" s="25" t="s">
-        <v>218</v>
       </c>
       <c r="D111" s="29">
         <v>115</v>
@@ -4065,10 +4060,10 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C112" s="25" t="s">
         <v>219</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>220</v>
       </c>
       <c r="D112" s="29">
         <v>135</v>
@@ -4082,10 +4077,10 @@
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C113" s="25" t="s">
         <v>221</v>
-      </c>
-      <c r="C113" s="25" t="s">
-        <v>222</v>
       </c>
       <c r="D113" s="29">
         <v>115</v>
@@ -4099,10 +4094,10 @@
     </row>
     <row r="114" spans="2:6">
       <c r="B114" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C114" s="25" t="s">
         <v>223</v>
-      </c>
-      <c r="C114" s="25" t="s">
-        <v>224</v>
       </c>
       <c r="D114" s="29">
         <v>130</v>
@@ -4116,10 +4111,10 @@
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C115" s="25" t="s">
         <v>225</v>
-      </c>
-      <c r="C115" s="25" t="s">
-        <v>226</v>
       </c>
       <c r="D115" s="29">
         <v>145</v>
@@ -4133,10 +4128,10 @@
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="C116" s="25" t="s">
         <v>227</v>
-      </c>
-      <c r="C116" s="25" t="s">
-        <v>228</v>
       </c>
       <c r="D116" s="29">
         <v>160</v>
@@ -4150,10 +4145,10 @@
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C117" s="25" t="s">
         <v>229</v>
-      </c>
-      <c r="C117" s="25" t="s">
-        <v>230</v>
       </c>
       <c r="D117" s="29">
         <v>75</v>
@@ -4167,10 +4162,10 @@
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C118" s="25" t="s">
         <v>231</v>
-      </c>
-      <c r="C118" s="25" t="s">
-        <v>232</v>
       </c>
       <c r="D118" s="29">
         <v>90</v>
@@ -4184,10 +4179,10 @@
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="C119" s="25" t="s">
         <v>233</v>
-      </c>
-      <c r="C119" s="25" t="s">
-        <v>234</v>
       </c>
       <c r="D119" s="29">
         <v>100</v>
@@ -4201,10 +4196,10 @@
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="C120" s="25" t="s">
         <v>235</v>
-      </c>
-      <c r="C120" s="25" t="s">
-        <v>236</v>
       </c>
       <c r="D120" s="29">
         <v>110</v>
@@ -4218,10 +4213,10 @@
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121" s="29">
         <v>130</v>
@@ -4230,15 +4225,15 @@
         <v>118.18181818181817</v>
       </c>
       <c r="F121" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D122" s="29">
         <v>140</v>
@@ -4252,10 +4247,10 @@
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C123" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D123" s="29">
         <v>150</v>
@@ -4269,10 +4264,10 @@
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D124" s="29">
         <v>175</v>
@@ -4286,10 +4281,10 @@
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="C125" s="25" t="s">
         <v>241</v>
-      </c>
-      <c r="C125" s="25" t="s">
-        <v>242</v>
       </c>
       <c r="D125" s="29">
         <v>80</v>
@@ -4303,10 +4298,10 @@
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="C126" s="25" t="s">
         <v>243</v>
-      </c>
-      <c r="C126" s="25" t="s">
-        <v>244</v>
       </c>
       <c r="D126" s="29">
         <v>100</v>
@@ -4320,10 +4315,10 @@
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C127" s="25" t="s">
         <v>245</v>
-      </c>
-      <c r="C127" s="25" t="s">
-        <v>246</v>
       </c>
       <c r="D127" s="29">
         <v>125</v>
@@ -4337,10 +4332,10 @@
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="C128" s="25" t="s">
         <v>247</v>
-      </c>
-      <c r="C128" s="25" t="s">
-        <v>248</v>
       </c>
       <c r="D128" s="29">
         <v>140</v>
@@ -4354,10 +4349,10 @@
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="C129" s="25" t="s">
         <v>249</v>
-      </c>
-      <c r="C129" s="25" t="s">
-        <v>250</v>
       </c>
       <c r="D129" s="29">
         <v>125</v>
@@ -4366,15 +4361,15 @@
         <v>113.63636363636363</v>
       </c>
       <c r="F129" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="C130" s="25" t="s">
         <v>251</v>
-      </c>
-      <c r="C130" s="25" t="s">
-        <v>252</v>
       </c>
       <c r="D130" s="29">
         <v>135</v>
@@ -4388,10 +4383,10 @@
     </row>
     <row r="131" spans="2:6">
       <c r="B131" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C131" s="25" t="s">
         <v>253</v>
-      </c>
-      <c r="C131" s="25" t="s">
-        <v>254</v>
       </c>
       <c r="D131" s="29">
         <v>145</v>
@@ -4405,10 +4400,10 @@
     </row>
     <row r="132" spans="2:6" ht="15" thickBot="1">
       <c r="B132" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="C132" s="26" t="s">
-        <v>256</v>
       </c>
       <c r="D132" s="30">
         <v>155</v>
@@ -4454,16 +4449,16 @@
     </row>
     <row r="2" spans="2:11">
       <c r="B2" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="D2" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="E2" s="46" t="s">
         <v>259</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>260</v>
       </c>
       <c r="F2" s="46"/>
       <c r="G2" s="46"/>
@@ -4477,36 +4472,36 @@
       <c r="C3" s="46"/>
       <c r="D3" s="47"/>
       <c r="E3" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="E4" s="8">
         <v>50</v>
@@ -4526,13 +4521,13 @@
     </row>
     <row r="5" spans="2:11">
       <c r="B5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>270</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>271</v>
       </c>
       <c r="E5" s="8">
         <v>65</v>
@@ -4552,13 +4547,13 @@
     </row>
     <row r="6" spans="2:11">
       <c r="B6" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>272</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>273</v>
       </c>
       <c r="E6" s="8">
         <v>80</v>
@@ -4578,13 +4573,13 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>274</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>275</v>
       </c>
       <c r="E7" s="8">
         <v>95</v>
@@ -4604,16 +4599,16 @@
     </row>
     <row r="8" spans="2:11">
       <c r="B8" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="8">
         <v>0</v>
@@ -4630,13 +4625,13 @@
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E9" s="8">
         <v>140</v>
@@ -4656,13 +4651,13 @@
     </row>
     <row r="10" spans="2:11">
       <c r="B10" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E10" s="8">
         <v>150</v>
@@ -4682,13 +4677,13 @@
     </row>
     <row r="11" spans="2:11">
       <c r="B11" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E11" s="8">
         <v>175</v>
@@ -4708,13 +4703,13 @@
     </row>
     <row r="12" spans="2:11">
       <c r="B12" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E12" s="8">
         <v>108</v>
@@ -4734,13 +4729,13 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E13" s="8">
         <v>119</v>
@@ -4760,13 +4755,13 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E14" s="8">
         <v>127</v>
@@ -4786,13 +4781,13 @@
     </row>
     <row r="15" spans="2:11">
       <c r="B15" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E15" s="8">
         <v>136</v>
@@ -4812,13 +4807,13 @@
     </row>
     <row r="16" spans="2:11">
       <c r="B16" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E16" s="8">
         <v>108</v>
@@ -4838,13 +4833,13 @@
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E17" s="8">
         <v>119</v>
@@ -4864,13 +4859,13 @@
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E18" s="8">
         <v>134</v>
@@ -4890,13 +4885,13 @@
     </row>
     <row r="19" spans="2:11">
       <c r="B19" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E19" s="8">
         <v>145</v>
@@ -4916,13 +4911,13 @@
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E20" s="8">
         <v>80</v>
@@ -4942,13 +4937,13 @@
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E21" s="8">
         <v>100</v>
@@ -4968,13 +4963,13 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E22" s="9">
         <v>125</v>
@@ -4988,13 +4983,13 @@
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E23" s="9">
         <v>140</v>
@@ -5008,13 +5003,13 @@
     </row>
     <row r="24" spans="2:11">
       <c r="B24" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E24" s="9">
         <v>70</v>
@@ -5028,13 +5023,13 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E25" s="9">
         <v>95</v>
@@ -5048,13 +5043,13 @@
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E26" s="9">
         <v>125</v>
@@ -5068,13 +5063,13 @@
     </row>
     <row r="27" spans="2:11">
       <c r="B27" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E27" s="9">
         <v>150</v>
@@ -5088,13 +5083,13 @@
     </row>
     <row r="28" spans="2:11">
       <c r="B28" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E28" s="9">
         <v>85</v>
@@ -5108,13 +5103,13 @@
     </row>
     <row r="29" spans="2:11">
       <c r="B29" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E29" s="9">
         <v>110</v>
@@ -5128,13 +5123,13 @@
     </row>
     <row r="30" spans="2:11">
       <c r="B30" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E30" s="10">
         <v>140</v>
@@ -5148,13 +5143,13 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E31" s="9">
         <v>170</v>
@@ -5168,13 +5163,13 @@
     </row>
     <row r="32" spans="2:11">
       <c r="B32" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E32" s="9">
         <v>65</v>
@@ -5188,13 +5183,13 @@
     </row>
     <row r="33" spans="2:11">
       <c r="B33" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E33" s="9">
         <v>100</v>
@@ -5208,13 +5203,13 @@
     </row>
     <row r="34" spans="2:11">
       <c r="B34" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E34" s="9">
         <v>115</v>
@@ -5228,16 +5223,16 @@
     </row>
     <row r="35" spans="2:11">
       <c r="B35" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
@@ -5248,13 +5243,13 @@
     </row>
     <row r="36" spans="2:11">
       <c r="B36" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E36" s="9">
         <v>115</v>
@@ -5268,13 +5263,13 @@
     </row>
     <row r="37" spans="2:11">
       <c r="B37" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E37" s="9">
         <v>125</v>
@@ -5288,13 +5283,13 @@
     </row>
     <row r="38" spans="2:11">
       <c r="B38" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E38" s="9">
         <v>135</v>
@@ -5308,16 +5303,16 @@
     </row>
     <row r="39" spans="2:11">
       <c r="B39" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
@@ -5328,13 +5323,13 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E40" s="8">
         <v>105</v>
@@ -5348,13 +5343,13 @@
     </row>
     <row r="41" spans="2:11">
       <c r="B41" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E41" s="8">
         <v>125</v>
@@ -5368,13 +5363,13 @@
     </row>
     <row r="42" spans="2:11">
       <c r="B42" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E42" s="8">
         <v>145</v>
@@ -5388,13 +5383,13 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E43" s="8">
         <v>165</v>
@@ -5408,13 +5403,13 @@
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E44" s="8">
         <v>125</v>
@@ -5428,13 +5423,13 @@
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E45" s="8">
         <v>150</v>
@@ -5448,13 +5443,13 @@
     </row>
     <row r="46" spans="2:11">
       <c r="B46" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E46" s="8">
         <v>175</v>
@@ -5468,13 +5463,13 @@
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E47" s="8">
         <v>200</v>
@@ -5488,13 +5483,13 @@
     </row>
     <row r="48" spans="2:11">
       <c r="B48" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E48" s="11">
         <v>50</v>
@@ -5508,13 +5503,13 @@
     </row>
     <row r="49" spans="2:11">
       <c r="B49" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E49" s="11">
         <v>65</v>
@@ -5528,13 +5523,13 @@
     </row>
     <row r="50" spans="2:11">
       <c r="B50" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E50" s="11">
         <v>80</v>
@@ -5548,13 +5543,13 @@
     </row>
     <row r="51" spans="2:11">
       <c r="B51" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E51" s="11">
         <v>95</v>
@@ -5568,13 +5563,13 @@
     </row>
     <row r="52" spans="2:11">
       <c r="B52" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E52" s="14">
         <v>108</v>
@@ -5588,13 +5583,13 @@
     </row>
     <row r="53" spans="2:11">
       <c r="B53" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E53" s="14">
         <v>119</v>
@@ -5608,13 +5603,13 @@
     </row>
     <row r="54" spans="2:11">
       <c r="B54" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E54" s="14">
         <v>134</v>
@@ -5628,13 +5623,13 @@
     </row>
     <row r="55" spans="2:11">
       <c r="B55" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E55" s="14">
         <v>145</v>
@@ -5648,13 +5643,13 @@
     </row>
     <row r="56" spans="2:11">
       <c r="B56" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E56" s="14">
         <v>108</v>
@@ -5668,13 +5663,13 @@
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E57" s="14">
         <v>115</v>
@@ -5688,13 +5683,13 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E58" s="14">
         <v>135</v>
@@ -5708,13 +5703,13 @@
     </row>
     <row r="59" spans="2:11">
       <c r="B59" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E59" s="14">
         <v>145</v>
@@ -5728,13 +5723,13 @@
     </row>
     <row r="60" spans="2:11">
       <c r="B60" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E60" s="14">
         <v>115</v>
@@ -5748,13 +5743,13 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E61" s="14">
         <v>80</v>
@@ -5768,13 +5763,13 @@
     </row>
     <row r="62" spans="2:11">
       <c r="B62" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E62" s="14">
         <v>100</v>
@@ -5788,13 +5783,13 @@
     </row>
     <row r="63" spans="2:11">
       <c r="B63" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E63" s="14">
         <v>115</v>
@@ -5808,13 +5803,13 @@
     </row>
     <row r="64" spans="2:11">
       <c r="B64" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E64" s="14">
         <v>135</v>
@@ -5828,13 +5823,13 @@
     </row>
     <row r="65" spans="2:11">
       <c r="B65" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E65" s="14">
         <v>105</v>
@@ -5848,13 +5843,13 @@
     </row>
     <row r="66" spans="2:11">
       <c r="B66" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E66" s="14">
         <v>115</v>
@@ -5868,13 +5863,13 @@
     </row>
     <row r="67" spans="2:11">
       <c r="B67" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E67" s="14">
         <v>128</v>
@@ -5888,16 +5883,16 @@
     </row>
     <row r="68" spans="2:11">
       <c r="B68" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
@@ -5908,13 +5903,13 @@
     </row>
     <row r="69" spans="2:11">
       <c r="B69" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E69" s="14">
         <v>80</v>
@@ -5928,13 +5923,13 @@
     </row>
     <row r="70" spans="2:11">
       <c r="B70" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E70" s="14">
         <v>90</v>
@@ -5948,13 +5943,13 @@
     </row>
     <row r="71" spans="2:11">
       <c r="B71" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E71" s="14">
         <v>100</v>
@@ -5968,13 +5963,13 @@
     </row>
     <row r="72" spans="2:11">
       <c r="B72" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E72" s="14">
         <v>110</v>
@@ -5988,13 +5983,13 @@
     </row>
     <row r="73" spans="2:11">
       <c r="B73" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E73" s="14">
         <v>108</v>
@@ -6008,13 +6003,13 @@
     </row>
     <row r="74" spans="2:11">
       <c r="B74" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E74" s="14">
         <v>119</v>
@@ -6028,13 +6023,13 @@
     </row>
     <row r="75" spans="2:11">
       <c r="B75" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E75" s="14">
         <v>134</v>
@@ -6048,13 +6043,13 @@
     </row>
     <row r="76" spans="2:11">
       <c r="B76" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E76" s="14">
         <v>145</v>
@@ -6068,13 +6063,13 @@
     </row>
     <row r="77" spans="2:11">
       <c r="B77" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E77" s="14">
         <v>115</v>
@@ -6088,13 +6083,13 @@
     </row>
     <row r="78" spans="2:11">
       <c r="B78" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E78" s="14">
         <v>130</v>
@@ -6108,13 +6103,13 @@
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E79" s="14">
         <v>145</v>
@@ -6128,13 +6123,13 @@
     </row>
     <row r="80" spans="2:11">
       <c r="B80" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E80" s="14">
         <v>160</v>
@@ -6148,13 +6143,13 @@
     </row>
     <row r="81" spans="2:11">
       <c r="B81" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E81" s="14">
         <v>115</v>
@@ -6168,13 +6163,13 @@
     </row>
     <row r="82" spans="2:11">
       <c r="B82" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E82" s="14">
         <v>130</v>
@@ -6188,13 +6183,13 @@
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E83" s="14">
         <v>145</v>
@@ -6208,13 +6203,13 @@
     </row>
     <row r="84" spans="2:11">
       <c r="B84" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E84" s="14">
         <v>160</v>
@@ -6228,16 +6223,16 @@
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F85" s="12"/>
       <c r="G85" s="12"/>
@@ -6248,13 +6243,13 @@
     </row>
     <row r="86" spans="2:11">
       <c r="B86" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E86" s="14">
         <v>100</v>
@@ -6268,13 +6263,13 @@
     </row>
     <row r="87" spans="2:11">
       <c r="B87" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E87" s="14">
         <v>110</v>
@@ -6288,13 +6283,13 @@
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E88" s="14">
         <v>120</v>
@@ -6308,13 +6303,13 @@
     </row>
     <row r="89" spans="2:11">
       <c r="B89" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E89" s="14">
         <v>70</v>
@@ -6328,13 +6323,13 @@
     </row>
     <row r="90" spans="2:11">
       <c r="B90" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E90" s="14">
         <v>80</v>
@@ -6348,13 +6343,13 @@
     </row>
     <row r="91" spans="2:11">
       <c r="B91" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E91" s="14">
         <v>95</v>
@@ -6368,13 +6363,13 @@
     </row>
     <row r="92" spans="2:11">
       <c r="B92" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E92" s="14">
         <v>110</v>
@@ -6388,13 +6383,13 @@
     </row>
     <row r="93" spans="2:11">
       <c r="B93" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E93" s="14">
         <v>100</v>
@@ -6408,13 +6403,13 @@
     </row>
     <row r="94" spans="2:11">
       <c r="B94" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E94" s="14">
         <v>115</v>
@@ -6428,13 +6423,13 @@
     </row>
     <row r="95" spans="2:11">
       <c r="B95" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E95" s="14">
         <v>135</v>
@@ -6448,13 +6443,13 @@
     </row>
     <row r="96" spans="2:11">
       <c r="B96" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E96" s="14">
         <v>150</v>
@@ -6468,13 +6463,13 @@
     </row>
     <row r="97" spans="2:11">
       <c r="B97" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E97" s="14">
         <v>95</v>
@@ -6488,13 +6483,13 @@
     </row>
     <row r="98" spans="2:11">
       <c r="B98" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E98" s="14">
         <v>110</v>
@@ -6508,13 +6503,13 @@
     </row>
     <row r="99" spans="2:11">
       <c r="B99" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E99" s="14">
         <v>125</v>
@@ -6528,13 +6523,13 @@
     </row>
     <row r="100" spans="2:11">
       <c r="B100" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E100" s="14">
         <v>140</v>
@@ -6548,13 +6543,13 @@
     </row>
     <row r="101" spans="2:11">
       <c r="B101" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E101" s="14">
         <v>110</v>
@@ -6568,13 +6563,13 @@
     </row>
     <row r="102" spans="2:11">
       <c r="B102" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E102" s="14">
         <v>122</v>
@@ -6588,13 +6583,13 @@
     </row>
     <row r="103" spans="2:11">
       <c r="B103" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E103" s="14">
         <v>132</v>
@@ -6608,16 +6603,16 @@
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E104" s="14" t="s">
         <v>371</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>372</v>
       </c>
       <c r="F104" s="12"/>
       <c r="G104" s="12"/>
@@ -6628,16 +6623,16 @@
     </row>
     <row r="105" spans="2:11">
       <c r="B105" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F105" s="12"/>
       <c r="G105" s="12"/>
@@ -6648,13 +6643,13 @@
     </row>
     <row r="106" spans="2:11">
       <c r="B106" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E106" s="14">
         <v>90</v>
@@ -6668,13 +6663,13 @@
     </row>
     <row r="107" spans="2:11">
       <c r="B107" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E107" s="14">
         <v>100</v>
@@ -6688,13 +6683,13 @@
     </row>
     <row r="108" spans="2:11">
       <c r="B108" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E108" s="14">
         <v>110</v>
@@ -6708,13 +6703,13 @@
     </row>
     <row r="109" spans="2:11">
       <c r="B109" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E109" s="14">
         <v>90</v>
@@ -6728,13 +6723,13 @@
     </row>
     <row r="110" spans="2:11">
       <c r="B110" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E110" s="14">
         <v>122</v>
@@ -6748,13 +6743,13 @@
     </row>
     <row r="111" spans="2:11">
       <c r="B111" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E111" s="14">
         <v>132</v>
@@ -6768,16 +6763,16 @@
     </row>
     <row r="112" spans="2:11">
       <c r="B112" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E112" s="14" t="s">
         <v>380</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="E112" s="14" t="s">
-        <v>381</v>
       </c>
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
@@ -6788,13 +6783,13 @@
     </row>
     <row r="113" spans="2:11">
       <c r="B113" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E113" s="14">
         <v>55</v>
@@ -6808,13 +6803,13 @@
     </row>
     <row r="114" spans="2:11">
       <c r="B114" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E114" s="14">
         <v>80</v>
@@ -6828,13 +6823,13 @@
     </row>
     <row r="115" spans="2:11">
       <c r="B115" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E115" s="14">
         <v>105</v>
@@ -6848,13 +6843,13 @@
     </row>
     <row r="116" spans="2:11">
       <c r="B116" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E116" s="14">
         <v>125</v>
@@ -6868,13 +6863,13 @@
     </row>
     <row r="117" spans="2:11">
       <c r="B117" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E117" s="14">
         <v>70</v>
@@ -6888,13 +6883,13 @@
     </row>
     <row r="118" spans="2:11">
       <c r="B118" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E118" s="14">
         <v>90</v>
@@ -6908,13 +6903,13 @@
     </row>
     <row r="119" spans="2:11">
       <c r="B119" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E119" s="14">
         <v>110</v>
@@ -6928,13 +6923,13 @@
     </row>
     <row r="120" spans="2:11">
       <c r="B120" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E120" s="14">
         <v>135</v>
@@ -6948,13 +6943,13 @@
     </row>
     <row r="121" spans="2:11">
       <c r="B121" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E121" s="14">
         <v>105</v>
@@ -6968,13 +6963,13 @@
     </row>
     <row r="122" spans="2:11">
       <c r="B122" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E122" s="14">
         <v>110</v>
@@ -6988,13 +6983,13 @@
     </row>
     <row r="123" spans="2:11">
       <c r="B123" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E123" s="14">
         <v>120</v>
@@ -7008,16 +7003,16 @@
     </row>
     <row r="124" spans="2:11">
       <c r="B124" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F124" s="12"/>
       <c r="G124" s="12"/>
@@ -7028,16 +7023,16 @@
     </row>
     <row r="125" spans="2:11">
       <c r="B125" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F125" s="12"/>
       <c r="G125" s="12"/>
@@ -7048,13 +7043,13 @@
     </row>
     <row r="126" spans="2:11">
       <c r="B126" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E126" s="14">
         <v>122</v>
@@ -7068,13 +7063,13 @@
     </row>
     <row r="127" spans="2:11">
       <c r="B127" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E127" s="14">
         <v>132</v>
@@ -7088,16 +7083,16 @@
     </row>
     <row r="128" spans="2:11">
       <c r="B128" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
@@ -7108,13 +7103,13 @@
     </row>
     <row r="129" spans="2:11">
       <c r="B129" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E129" s="14">
         <v>95</v>
@@ -7128,13 +7123,13 @@
     </row>
     <row r="130" spans="2:11">
       <c r="B130" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E130" s="14">
         <v>110</v>
@@ -7148,13 +7143,13 @@
     </row>
     <row r="131" spans="2:11">
       <c r="B131" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E131" s="14">
         <v>127</v>
@@ -7168,13 +7163,13 @@
     </row>
     <row r="132" spans="2:11">
       <c r="B132" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E132" s="14">
         <v>140</v>
@@ -7188,16 +7183,16 @@
     </row>
     <row r="133" spans="2:11">
       <c r="B133" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F133" s="12"/>
       <c r="G133" s="12"/>
@@ -7208,16 +7203,16 @@
     </row>
     <row r="134" spans="2:11">
       <c r="B134" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F134" s="12"/>
       <c r="G134" s="12"/>
@@ -7228,13 +7223,13 @@
     </row>
     <row r="135" spans="2:11">
       <c r="B135" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E135" s="14">
         <v>125</v>
@@ -7248,13 +7243,13 @@
     </row>
     <row r="136" spans="2:11">
       <c r="B136" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E136" s="14">
         <v>150</v>
@@ -7268,16 +7263,16 @@
     </row>
     <row r="137" spans="2:11">
       <c r="B137" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E137" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F137" s="12"/>
       <c r="G137" s="12"/>
@@ -7288,13 +7283,13 @@
     </row>
     <row r="138" spans="2:11">
       <c r="B138" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E138" s="14">
         <v>134</v>
@@ -7308,13 +7303,13 @@
     </row>
     <row r="139" spans="2:11">
       <c r="B139" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E139" s="14">
         <v>145</v>
@@ -7328,13 +7323,13 @@
     </row>
     <row r="140" spans="2:11">
       <c r="B140" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E140" s="14">
         <v>155</v>
@@ -7348,16 +7343,16 @@
     </row>
     <row r="141" spans="2:11">
       <c r="B141" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F141" s="12"/>
       <c r="G141" s="12"/>
@@ -7368,13 +7363,13 @@
     </row>
     <row r="142" spans="2:11">
       <c r="B142" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E142" s="14">
         <v>160</v>
@@ -7388,13 +7383,13 @@
     </row>
     <row r="143" spans="2:11">
       <c r="B143" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E143" s="14">
         <v>180</v>
@@ -7408,13 +7403,13 @@
     </row>
     <row r="144" spans="2:11">
       <c r="B144" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E144" s="14">
         <v>200</v>
@@ -7428,13 +7423,13 @@
     </row>
     <row r="145" spans="2:11">
       <c r="B145" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E145" s="14">
         <v>105</v>
@@ -7448,13 +7443,13 @@
     </row>
     <row r="146" spans="2:11">
       <c r="B146" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E146" s="14">
         <v>115</v>
@@ -7468,13 +7463,13 @@
     </row>
     <row r="147" spans="2:11">
       <c r="B147" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E147" s="14">
         <v>128</v>
@@ -7488,13 +7483,13 @@
     </row>
     <row r="148" spans="2:11">
       <c r="B148" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E148" s="14">
         <v>138</v>
